--- a/artfynd/A 5766-2026 artfynd.xlsx
+++ b/artfynd/A 5766-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5007767</v>
+        <v>66242673</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>Gruvberget, Butorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420355.107380996</v>
+        <v>420416</v>
       </c>
       <c r="R2" t="n">
-        <v>6618792.907299347</v>
+        <v>6618892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett blommande exemplar och en fjolårsståndare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +776,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Lars Efraimsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Flora Värmland</t>
+          <t>Lars Efraimsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5209210</v>
+        <v>5007767</v>
       </c>
       <c r="B3" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +799,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>, Vrm</t>
+          <t>Skymmelån, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420355.107380996</v>
+        <v>420355</v>
       </c>
       <c r="R3" t="n">
-        <v>6618792.907299347</v>
+        <v>6618793</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +856,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66242673</v>
+        <v>5209210</v>
       </c>
       <c r="B4" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,45 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gruvberget, Butorp, Vrm</t>
+          <t>Skymmelån, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>420415.8882696612</v>
+        <v>420355</v>
       </c>
       <c r="R4" t="n">
-        <v>6618892.082086471</v>
+        <v>6618793</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,27 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-06-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett blommande exemplar och en fjolårsståndare.</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,12 +970,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Efraimsson</t>
+          <t>Flora Värmland</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Efraimsson</t>
+          <t>Flora Värmland</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 5766-2026 artfynd.xlsx
+++ b/artfynd/A 5766-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66242673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5007767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,8 +994,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5209210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>